--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/64.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/64.xlsx
@@ -426,13 +426,13 @@
         <v>-2.814373904262876</v>
       </c>
       <c r="E2">
-        <v>-13.68236967127488</v>
+        <v>-25.16205128071924</v>
       </c>
       <c r="F2">
-        <v>-5.496556096097696</v>
+        <v>-5.841821406428566</v>
       </c>
       <c r="G2">
-        <v>-4.200626584719051</v>
+        <v>-13.92372862846838</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-2.630100401468725</v>
       </c>
       <c r="E3">
-        <v>-14.6581697789217</v>
+        <v>-24.7396669246018</v>
       </c>
       <c r="F3">
-        <v>-5.602239959246801</v>
+        <v>-5.535549311294688</v>
       </c>
       <c r="G3">
-        <v>-4.437476254780669</v>
+        <v>-12.49155683326981</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-2.478424804518087</v>
       </c>
       <c r="E4">
-        <v>-14.42491713973461</v>
+        <v>-23.76363133630658</v>
       </c>
       <c r="F4">
-        <v>-5.348669637713961</v>
+        <v>-6.017677694984877</v>
       </c>
       <c r="G4">
-        <v>-3.072084784200278</v>
+        <v>-13.78809888826998</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-2.358781630701549</v>
       </c>
       <c r="E5">
-        <v>-16.21404476458105</v>
+        <v>-25.31606468172011</v>
       </c>
       <c r="F5">
-        <v>-5.692723413019519</v>
+        <v>-6.153630137442819</v>
       </c>
       <c r="G5">
-        <v>-3.627640673327533</v>
+        <v>-12.96886135748531</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-2.251882824707715</v>
       </c>
       <c r="E6">
-        <v>-15.48562160655124</v>
+        <v>-26.55889984465123</v>
       </c>
       <c r="F6">
-        <v>-5.607721957273095</v>
+        <v>-6.386323255745379</v>
       </c>
       <c r="G6">
-        <v>-2.990562600295725</v>
+        <v>-13.6700051077931</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-2.139636574662302</v>
       </c>
       <c r="E7">
-        <v>-16.48343915482335</v>
+        <v>-26.68057088428932</v>
       </c>
       <c r="F7">
-        <v>-5.441857269337291</v>
+        <v>-6.099545392651125</v>
       </c>
       <c r="G7">
-        <v>-3.470638051127597</v>
+        <v>-12.55525172944539</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-2.000826690612356</v>
       </c>
       <c r="E8">
-        <v>-16.74721823729614</v>
+        <v>-26.61657448961292</v>
       </c>
       <c r="F8">
-        <v>-5.373752372002691</v>
+        <v>-5.810932014400877</v>
       </c>
       <c r="G8">
-        <v>-3.547452639275306</v>
+        <v>-12.12326857366251</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-1.820207647776875</v>
       </c>
       <c r="E9">
-        <v>-17.49712900449234</v>
+        <v>-28.73134920882494</v>
       </c>
       <c r="F9">
-        <v>-5.496742973395718</v>
+        <v>-6.029116010959139</v>
       </c>
       <c r="G9">
-        <v>-3.066675352789109</v>
+        <v>-12.36839460757231</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-1.577797872060904</v>
       </c>
       <c r="E10">
-        <v>-17.9890707213676</v>
+        <v>-28.8113809299625</v>
       </c>
       <c r="F10">
-        <v>-5.193039649256684</v>
+        <v>-6.112292245638018</v>
       </c>
       <c r="G10">
-        <v>-4.096933677337999</v>
+        <v>-13.39951698450695</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-1.265984063139321</v>
       </c>
       <c r="E11">
-        <v>-18.48549562751045</v>
+        <v>-29.44999539147218</v>
       </c>
       <c r="F11">
-        <v>-5.26045484266511</v>
+        <v>-5.793993487782294</v>
       </c>
       <c r="G11">
-        <v>-2.683953114630585</v>
+        <v>-11.86329143246354</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-0.8787816806546377</v>
       </c>
       <c r="E12">
-        <v>-19.59272563628188</v>
+        <v>-28.37433790348223</v>
       </c>
       <c r="F12">
-        <v>-5.134616738036122</v>
+        <v>-5.103173840790988</v>
       </c>
       <c r="G12">
-        <v>-2.705110811172067</v>
+        <v>-12.03449298448141</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-0.4169768823245444</v>
       </c>
       <c r="E13">
-        <v>-19.81817571475375</v>
+        <v>-30.13530521271197</v>
       </c>
       <c r="F13">
-        <v>-5.385389443069339</v>
+        <v>-5.561981363023373</v>
       </c>
       <c r="G13">
-        <v>-2.063633023118568</v>
+        <v>-10.85594539359195</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>0.1035085265674055</v>
       </c>
       <c r="E14">
-        <v>-21.27749457762155</v>
+        <v>-30.94725833805026</v>
       </c>
       <c r="F14">
-        <v>-5.359054789254454</v>
+        <v>-6.031117815236254</v>
       </c>
       <c r="G14">
-        <v>-1.767210086077765</v>
+        <v>-12.34254586800168</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>0.6686890241068307</v>
       </c>
       <c r="E15">
-        <v>-21.7712612695219</v>
+        <v>-29.9633477334557</v>
       </c>
       <c r="F15">
-        <v>-4.944892728631265</v>
+        <v>-4.902462871597769</v>
       </c>
       <c r="G15">
-        <v>-1.426270243170382</v>
+        <v>-11.24969174839625</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>1.253426895442572</v>
       </c>
       <c r="E16">
-        <v>-22.49830777145337</v>
+        <v>-30.69917947496206</v>
       </c>
       <c r="F16">
-        <v>-5.383359132085746</v>
+        <v>-5.27759212437608</v>
       </c>
       <c r="G16">
-        <v>-1.104832824034846</v>
+        <v>-10.9466477202769</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>1.830967889206888</v>
       </c>
       <c r="E17">
-        <v>-23.95035390506486</v>
+        <v>-30.56866432558699</v>
       </c>
       <c r="F17">
-        <v>-4.755936024742438</v>
+        <v>-4.827382541558616</v>
       </c>
       <c r="G17">
-        <v>-1.107295869916064</v>
+        <v>-10.60737308177577</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>2.377193208329714</v>
       </c>
       <c r="E18">
-        <v>-23.15175298533818</v>
+        <v>-32.9090204490171</v>
       </c>
       <c r="F18">
-        <v>-4.824961055213909</v>
+        <v>-4.602634875833815</v>
       </c>
       <c r="G18">
-        <v>-0.7479858098112659</v>
+        <v>-11.28064203864289</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>2.86276761725637</v>
       </c>
       <c r="E19">
-        <v>-24.73401991751424</v>
+        <v>-31.95267919418125</v>
       </c>
       <c r="F19">
-        <v>-4.294874097139425</v>
+        <v>-4.339915485227481</v>
       </c>
       <c r="G19">
-        <v>0.1220189368181235</v>
+        <v>-10.31868357911471</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>3.269276018908507</v>
       </c>
       <c r="E20">
-        <v>-27.23165900017875</v>
+        <v>-32.64239748486749</v>
       </c>
       <c r="F20">
-        <v>-4.02085496482643</v>
+        <v>-4.270826314666435</v>
       </c>
       <c r="G20">
-        <v>-0.962889873493055</v>
+        <v>-9.670733674531933</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>3.580664478715827</v>
       </c>
       <c r="E21">
-        <v>-25.68820109024843</v>
+        <v>-34.67754804560265</v>
       </c>
       <c r="F21">
-        <v>-3.740272955199854</v>
+        <v>-3.936376132032102</v>
       </c>
       <c r="G21">
-        <v>-0.2114423837160453</v>
+        <v>-9.583960965402095</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>3.786962210638686</v>
       </c>
       <c r="E22">
-        <v>-26.17060131238953</v>
+        <v>-34.58458753117318</v>
       </c>
       <c r="F22">
-        <v>-3.64698950936864</v>
+        <v>-3.833033778078974</v>
       </c>
       <c r="G22">
-        <v>-0.1178036031377598</v>
+        <v>-9.767414846460808</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>3.889239922417331</v>
       </c>
       <c r="E23">
-        <v>-27.46989748924828</v>
+        <v>-34.45882048679516</v>
       </c>
       <c r="F23">
-        <v>-3.479258424011491</v>
+        <v>-4.008773664250501</v>
       </c>
       <c r="G23">
-        <v>0.01179101254255006</v>
+        <v>-9.099167987176763</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>3.890814911102023</v>
       </c>
       <c r="E24">
-        <v>-28.43295899951152</v>
+        <v>-36.24769451709717</v>
       </c>
       <c r="F24">
-        <v>-3.151246797776376</v>
+        <v>-4.075817478621756</v>
       </c>
       <c r="G24">
-        <v>-0.6434685765909353</v>
+        <v>-8.780064502646413</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>3.804682309042596</v>
       </c>
       <c r="E25">
-        <v>-27.24279904623762</v>
+        <v>-36.31603145410992</v>
       </c>
       <c r="F25">
-        <v>-2.827180182976621</v>
+        <v>-4.730415395768089</v>
       </c>
       <c r="G25">
-        <v>0.215144582837822</v>
+        <v>-9.051277635405665</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>3.647312447112861</v>
       </c>
       <c r="E26">
-        <v>-27.30555011056191</v>
+        <v>-36.1812957669597</v>
       </c>
       <c r="F26">
-        <v>-2.835837511363371</v>
+        <v>-4.087989842287824</v>
       </c>
       <c r="G26">
-        <v>-1.220582738269924</v>
+        <v>-9.296906872237431</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>3.438479989232361</v>
       </c>
       <c r="E27">
-        <v>-28.16224682333299</v>
+        <v>-35.07063543912746</v>
       </c>
       <c r="F27">
-        <v>-3.202850271325055</v>
+        <v>-3.597596097424957</v>
       </c>
       <c r="G27">
-        <v>0.09179365604457757</v>
+        <v>-7.974923274767963</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>3.201189336180172</v>
       </c>
       <c r="E28">
-        <v>-27.96738658678293</v>
+        <v>-37.2151237405408</v>
       </c>
       <c r="F28">
-        <v>-3.263872043952853</v>
+        <v>-4.201217688565125</v>
       </c>
       <c r="G28">
-        <v>-1.654631674469309</v>
+        <v>-8.798150012927451</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>2.957166025435129</v>
       </c>
       <c r="E29">
-        <v>-29.08841032738173</v>
+        <v>-35.34973661340521</v>
       </c>
       <c r="F29">
-        <v>-3.309573045554688</v>
+        <v>-3.842837709548502</v>
       </c>
       <c r="G29">
-        <v>-0.2458124675047588</v>
+        <v>-9.620426624517167</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>2.728625445531774</v>
       </c>
       <c r="E30">
-        <v>-27.5982570849957</v>
+        <v>-35.5081969758816</v>
       </c>
       <c r="F30">
-        <v>-3.213581462608073</v>
+        <v>-4.210717548498889</v>
       </c>
       <c r="G30">
-        <v>-1.139802116566168</v>
+        <v>-9.14760457896184</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>2.532414159507061</v>
       </c>
       <c r="E31">
-        <v>-27.96490498302673</v>
+        <v>-35.2519125178915</v>
       </c>
       <c r="F31">
-        <v>-3.140667642261241</v>
+        <v>-4.410495714907913</v>
       </c>
       <c r="G31">
-        <v>-0.4484675126912445</v>
+        <v>-9.59761365520605</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>2.382721278525206</v>
       </c>
       <c r="E32">
-        <v>-27.77147121578909</v>
+        <v>-34.48413239226104</v>
       </c>
       <c r="F32">
-        <v>-3.296094916361341</v>
+        <v>-2.975076143595849</v>
       </c>
       <c r="G32">
-        <v>-1.699612056711386</v>
+        <v>-10.28356862257966</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>2.289806030507237</v>
       </c>
       <c r="E33">
-        <v>-27.54824461805499</v>
+        <v>-35.37322354384599</v>
       </c>
       <c r="F33">
-        <v>-3.161083195217171</v>
+        <v>-4.41682737115784</v>
       </c>
       <c r="G33">
-        <v>-1.049023647333813</v>
+        <v>-9.05752463483827</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>2.256207041285136</v>
       </c>
       <c r="E34">
-        <v>-26.81585904526847</v>
+        <v>-34.14300018102622</v>
       </c>
       <c r="F34">
-        <v>-3.42268607315312</v>
+        <v>-4.680796305731456</v>
       </c>
       <c r="G34">
-        <v>-1.654883275930293</v>
+        <v>-10.228338791348</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>2.28227502045394</v>
       </c>
       <c r="E35">
-        <v>-26.88433862921246</v>
+        <v>-34.72190444850778</v>
       </c>
       <c r="F35">
-        <v>-3.749097364560683</v>
+        <v>-3.898394113062117</v>
       </c>
       <c r="G35">
-        <v>-1.389135853856377</v>
+        <v>-10.21396440261648</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>2.362648321356886</v>
       </c>
       <c r="E36">
-        <v>-25.8895642154735</v>
+        <v>-34.22174807978261</v>
       </c>
       <c r="F36">
-        <v>-3.154092717306421</v>
+        <v>-4.234610127792165</v>
       </c>
       <c r="G36">
-        <v>-1.865907380240057</v>
+        <v>-9.705808904520511</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>2.48782657006891</v>
       </c>
       <c r="E37">
-        <v>-25.16102784559351</v>
+        <v>-33.83134380710734</v>
       </c>
       <c r="F37">
-        <v>-3.769282488305916</v>
+        <v>-4.053856228692357</v>
       </c>
       <c r="G37">
-        <v>-0.460925095555522</v>
+        <v>-8.947223878560832</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>2.650073839954361</v>
       </c>
       <c r="E38">
-        <v>-24.11916635912279</v>
+        <v>-34.34830760711198</v>
       </c>
       <c r="F38">
-        <v>-3.718539758922279</v>
+        <v>-3.773179196710855</v>
       </c>
       <c r="G38">
-        <v>-0.2231021251053585</v>
+        <v>-10.42365435707392</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>2.836677793034801</v>
       </c>
       <c r="E39">
-        <v>-23.49563624453265</v>
+        <v>-34.46613623655455</v>
       </c>
       <c r="F39">
-        <v>-3.065801904373629</v>
+        <v>-4.100201798601778</v>
       </c>
       <c r="G39">
-        <v>0.2242684463440534</v>
+        <v>-9.579124258369221</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>3.03748425103194</v>
       </c>
       <c r="E40">
-        <v>-24.22640515209843</v>
+        <v>-32.67309601016549</v>
       </c>
       <c r="F40">
-        <v>-3.122177875698485</v>
+        <v>-3.83543467624678</v>
       </c>
       <c r="G40">
-        <v>-1.131601895265393</v>
+        <v>-9.378329739775806</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>3.243882086513894</v>
       </c>
       <c r="E41">
-        <v>-24.54481574499976</v>
+        <v>-33.68696473455779</v>
       </c>
       <c r="F41">
-        <v>-3.132327846910536</v>
+        <v>-3.013584744782718</v>
       </c>
       <c r="G41">
-        <v>-0.4369865407610521</v>
+        <v>-10.232132676536</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>3.446037311364436</v>
       </c>
       <c r="E42">
-        <v>-23.28622602099595</v>
+        <v>-31.49650789349258</v>
       </c>
       <c r="F42">
-        <v>-3.169051611530704</v>
+        <v>-3.454643674820773</v>
       </c>
       <c r="G42">
-        <v>0.6052394059123031</v>
+        <v>-8.766143658653776</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>3.638753256144103</v>
       </c>
       <c r="E43">
-        <v>-22.80559190371785</v>
+        <v>-33.28442641577897</v>
       </c>
       <c r="F43">
-        <v>-2.730392787807497</v>
+        <v>-3.069167279443938</v>
       </c>
       <c r="G43">
-        <v>0.02433798013638785</v>
+        <v>-9.63776726205187</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>3.815157478162123</v>
       </c>
       <c r="E44">
-        <v>-22.01262893413073</v>
+        <v>-32.85543048761033</v>
       </c>
       <c r="F44">
-        <v>-2.860028619221709</v>
+        <v>-3.796825509734282</v>
       </c>
       <c r="G44">
-        <v>-0.700621834780913</v>
+        <v>-9.914515626952785</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>3.96854840612641</v>
       </c>
       <c r="E45">
-        <v>-22.42043613241747</v>
+        <v>-31.10365824485317</v>
       </c>
       <c r="F45">
-        <v>-3.394741582275191</v>
+        <v>-3.372313139100738</v>
       </c>
       <c r="G45">
-        <v>-1.794859762421758</v>
+        <v>-10.64483190455263</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>4.095061264444813</v>
       </c>
       <c r="E46">
-        <v>-21.17813080094525</v>
+        <v>-31.21515380339602</v>
       </c>
       <c r="F46">
-        <v>-2.926549018787912</v>
+        <v>-3.198256732317323</v>
       </c>
       <c r="G46">
-        <v>-0.5610790297550933</v>
+        <v>-9.247765134252489</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>4.188374055770016</v>
       </c>
       <c r="E47">
-        <v>-21.61683124891232</v>
+        <v>-30.77129542353421</v>
       </c>
       <c r="F47">
-        <v>-3.192935480441446</v>
+        <v>-3.660032911288199</v>
       </c>
       <c r="G47">
-        <v>-0.4157957387641772</v>
+        <v>-11.15277221718854</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>4.245611411812843</v>
       </c>
       <c r="E48">
-        <v>-21.5063545970212</v>
+        <v>-32.27557976906117</v>
       </c>
       <c r="F48">
-        <v>-2.8334453235781</v>
+        <v>-3.484137030084002</v>
       </c>
       <c r="G48">
-        <v>0.1762953309344746</v>
+        <v>-10.2072307529896</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>4.264427777559803</v>
       </c>
       <c r="E49">
-        <v>-19.92333593815987</v>
+        <v>-31.05252724483256</v>
       </c>
       <c r="F49">
-        <v>-3.064458129904379</v>
+        <v>-3.604355354272052</v>
       </c>
       <c r="G49">
-        <v>-0.6678772288519818</v>
+        <v>-9.753222537733953</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>4.24377545736473</v>
       </c>
       <c r="E50">
-        <v>-19.87691907958125</v>
+        <v>-30.38489432188172</v>
       </c>
       <c r="F50">
-        <v>-2.787772828682741</v>
+        <v>-3.134647976076655</v>
       </c>
       <c r="G50">
-        <v>-1.328834266858553</v>
+        <v>-9.17207944213367</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>4.187262059990366</v>
       </c>
       <c r="E51">
-        <v>-19.31269838906957</v>
+        <v>-29.05593664027273</v>
       </c>
       <c r="F51">
-        <v>-2.998034336399018</v>
+        <v>-3.398806163507166</v>
       </c>
       <c r="G51">
-        <v>-2.376784146769308</v>
+        <v>-9.916127862630409</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>4.097198680330227</v>
       </c>
       <c r="E52">
-        <v>-19.56456305642818</v>
+        <v>-29.72350842882446</v>
       </c>
       <c r="F52">
-        <v>-2.873066478170564</v>
+        <v>-3.824221246512511</v>
       </c>
       <c r="G52">
-        <v>-1.822853735501835</v>
+        <v>-10.49022611732312</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>3.980279538053115</v>
       </c>
       <c r="E53">
-        <v>-18.29668090376063</v>
+        <v>-28.12664848915869</v>
       </c>
       <c r="F53">
-        <v>-3.340762549853353</v>
+        <v>-4.162696417730934</v>
       </c>
       <c r="G53">
-        <v>-0.9052532756543437</v>
+        <v>-11.12588065577304</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>3.842071130195508</v>
       </c>
       <c r="E54">
-        <v>-18.87525685687663</v>
+        <v>-27.77861261929919</v>
       </c>
       <c r="F54">
-        <v>-2.662664020627814</v>
+        <v>-3.201834323980301</v>
       </c>
       <c r="G54">
-        <v>-1.566650616217638</v>
+        <v>-10.71638603583843</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>3.688442128975514</v>
       </c>
       <c r="E55">
-        <v>-19.03070578413793</v>
+        <v>-26.37487171792752</v>
       </c>
       <c r="F55">
-        <v>-3.206777861995345</v>
+        <v>-3.714115676447499</v>
       </c>
       <c r="G55">
-        <v>-0.6382908833675152</v>
+        <v>-10.55452684333239</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>3.526963074298937</v>
       </c>
       <c r="E56">
-        <v>-17.1425177903737</v>
+        <v>-27.55160021729467</v>
       </c>
       <c r="F56">
-        <v>-2.653602847232627</v>
+        <v>-3.358088292568261</v>
       </c>
       <c r="G56">
-        <v>-2.10019137750874</v>
+        <v>-10.51196978042505</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>3.360728173261459</v>
       </c>
       <c r="E57">
-        <v>-16.85194372719753</v>
+        <v>-28.0846197218935</v>
       </c>
       <c r="F57">
-        <v>-2.845129113969254</v>
+        <v>-3.748903360586042</v>
       </c>
       <c r="G57">
-        <v>-2.162449496920273</v>
+        <v>-11.37596588690067</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>3.196703032288581</v>
       </c>
       <c r="E58">
-        <v>-15.75071394648626</v>
+        <v>-27.05208236340458</v>
       </c>
       <c r="F58">
-        <v>-3.001082970286239</v>
+        <v>-3.500236984420359</v>
       </c>
       <c r="G58">
-        <v>-2.605456769348926</v>
+        <v>-10.26987951677477</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>3.03916895778881</v>
       </c>
       <c r="E59">
-        <v>-16.38334629383181</v>
+        <v>-26.70226227478606</v>
       </c>
       <c r="F59">
-        <v>-3.012986895799639</v>
+        <v>-3.49432976135577</v>
       </c>
       <c r="G59">
-        <v>-2.078993954420786</v>
+        <v>-11.254982000168</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>2.891892412021386</v>
       </c>
       <c r="E60">
-        <v>-16.59189157883305</v>
+        <v>-26.14764194917064</v>
       </c>
       <c r="F60">
-        <v>-2.941104068003758</v>
+        <v>-3.409017107396962</v>
       </c>
       <c r="G60">
-        <v>-2.907345417075065</v>
+        <v>-11.61547392503032</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>2.76118776548938</v>
       </c>
       <c r="E61">
-        <v>-15.63666432860308</v>
+        <v>-27.2580192473774</v>
       </c>
       <c r="F61">
-        <v>-3.369749119223641</v>
+        <v>-3.874651193977849</v>
       </c>
       <c r="G61">
-        <v>-1.770427936341936</v>
+        <v>-11.13131657154853</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>2.650493204750331</v>
       </c>
       <c r="E62">
-        <v>-15.87638362867312</v>
+        <v>-25.10266940105666</v>
       </c>
       <c r="F62">
-        <v>-2.882599595928552</v>
+        <v>-3.652066870533539</v>
       </c>
       <c r="G62">
-        <v>-2.960565747164389</v>
+        <v>-10.62013192428412</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>2.56493257418731</v>
       </c>
       <c r="E63">
-        <v>-15.90218687356882</v>
+        <v>-24.33622970373246</v>
       </c>
       <c r="F63">
-        <v>-3.084728773769046</v>
+        <v>-4.185107440140317</v>
       </c>
       <c r="G63">
-        <v>-2.216898039404667</v>
+        <v>-12.2873988004085</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>2.509829544410911</v>
       </c>
       <c r="E64">
-        <v>-15.61663488806715</v>
+        <v>-27.63425845335668</v>
       </c>
       <c r="F64">
-        <v>-3.293148431505666</v>
+        <v>-3.938419112663019</v>
       </c>
       <c r="G64">
-        <v>-2.359433577597987</v>
+        <v>-11.20578067236335</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>2.486377862675427</v>
       </c>
       <c r="E65">
-        <v>-14.61084269706753</v>
+        <v>-25.54791802243882</v>
       </c>
       <c r="F65">
-        <v>-3.009758511291016</v>
+        <v>-4.150250072941495</v>
       </c>
       <c r="G65">
-        <v>-2.671369731035815</v>
+        <v>-12.24629175644737</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>2.497317407043734</v>
       </c>
       <c r="E66">
-        <v>-13.87067720593584</v>
+        <v>-26.64240943382668</v>
       </c>
       <c r="F66">
-        <v>-2.957420198197573</v>
+        <v>-3.996562499789505</v>
       </c>
       <c r="G66">
-        <v>-2.612038133880997</v>
+        <v>-11.6686313547544</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>2.542796203103431</v>
       </c>
       <c r="E67">
-        <v>-14.04154558719326</v>
+        <v>-25.29836287682412</v>
       </c>
       <c r="F67">
-        <v>-3.057722628646015</v>
+        <v>-4.101052248678369</v>
       </c>
       <c r="G67">
-        <v>-3.446805433790384</v>
+        <v>-11.53788797977196</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>2.619677283317367</v>
       </c>
       <c r="E68">
-        <v>-15.31340374003954</v>
+        <v>-25.87701581399825</v>
       </c>
       <c r="F68">
-        <v>-2.860182238695506</v>
+        <v>-3.90193527948904</v>
       </c>
       <c r="G68">
-        <v>-3.290739695978061</v>
+        <v>-10.76666660148888</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>2.727479918746382</v>
       </c>
       <c r="E69">
-        <v>-14.29997654186299</v>
+        <v>-25.97931404183152</v>
       </c>
       <c r="F69">
-        <v>-2.882373125982644</v>
+        <v>-4.117514871669361</v>
       </c>
       <c r="G69">
-        <v>-3.388807986487892</v>
+        <v>-11.73608372011705</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>2.861644536948571</v>
       </c>
       <c r="E70">
-        <v>-16.12406851452264</v>
+        <v>-26.18700797371931</v>
       </c>
       <c r="F70">
-        <v>-3.005347890316517</v>
+        <v>-4.4905441304038</v>
       </c>
       <c r="G70">
-        <v>-2.779770234173711</v>
+        <v>-12.24684130700689</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>3.019094644220565</v>
       </c>
       <c r="E71">
-        <v>-15.29191613087314</v>
+        <v>-24.27398130002302</v>
       </c>
       <c r="F71">
-        <v>-3.222557115883826</v>
+        <v>-4.930102499086976</v>
       </c>
       <c r="G71">
-        <v>-3.000428026002753</v>
+        <v>-11.20050366277376</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>3.199361691277067</v>
       </c>
       <c r="E72">
-        <v>-15.10301989459119</v>
+        <v>-27.1685728287779</v>
       </c>
       <c r="F72">
-        <v>-3.221529290744706</v>
+        <v>-4.483447544196716</v>
       </c>
       <c r="G72">
-        <v>-3.750819451752736</v>
+        <v>-11.81725498619444</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>3.398238856518015</v>
       </c>
       <c r="E73">
-        <v>-15.12319877476937</v>
+        <v>-24.12993507031303</v>
       </c>
       <c r="F73">
-        <v>-2.980501128209188</v>
+        <v>-3.840748801446037</v>
       </c>
       <c r="G73">
-        <v>-2.832537019524154</v>
+        <v>-11.76854030858406</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>3.615608721065771</v>
       </c>
       <c r="E74">
-        <v>-14.17553860460621</v>
+        <v>-26.92689722793654</v>
       </c>
       <c r="F74">
-        <v>-2.990373950886037</v>
+        <v>-3.978628614003068</v>
       </c>
       <c r="G74">
-        <v>-3.92040876809298</v>
+        <v>-12.7140221829633</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>3.850051278423557</v>
       </c>
       <c r="E75">
-        <v>-14.46099096367971</v>
+        <v>-24.29287862205703</v>
       </c>
       <c r="F75">
-        <v>-3.492260649577248</v>
+        <v>-4.335544456900868</v>
       </c>
       <c r="G75">
-        <v>-2.952514500412881</v>
+        <v>-11.90743755722973</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>4.096391476937812</v>
       </c>
       <c r="E76">
-        <v>-16.59601701865403</v>
+        <v>-26.10492032538227</v>
       </c>
       <c r="F76">
-        <v>-3.736670816095187</v>
+        <v>-4.440710448215625</v>
       </c>
       <c r="G76">
-        <v>-2.993459327642587</v>
+        <v>-10.66894922880622</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>4.355069430048896</v>
       </c>
       <c r="E77">
-        <v>-16.2314295762965</v>
+        <v>-26.42271051734455</v>
       </c>
       <c r="F77">
-        <v>-3.509946685387918</v>
+        <v>-3.956901752549155</v>
       </c>
       <c r="G77">
-        <v>-3.176999282885321</v>
+        <v>-12.00544625791985</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>4.619593469265317</v>
       </c>
       <c r="E78">
-        <v>-15.87953997505646</v>
+        <v>-27.32802945553598</v>
       </c>
       <c r="F78">
-        <v>-3.269373046450131</v>
+        <v>-5.024797818741805</v>
       </c>
       <c r="G78">
-        <v>-2.418434120198878</v>
+        <v>-11.13962935139764</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>4.884689528808335</v>
       </c>
       <c r="E79">
-        <v>-17.15980750413499</v>
+        <v>-27.2340455059808</v>
       </c>
       <c r="F79">
-        <v>-3.748562071961264</v>
+        <v>-4.186767955792655</v>
       </c>
       <c r="G79">
-        <v>-4.20258311713276</v>
+        <v>-10.86294388686197</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>5.146450635379966</v>
       </c>
       <c r="E80">
-        <v>-16.58150778793346</v>
+        <v>-25.94214885565057</v>
       </c>
       <c r="F80">
-        <v>-3.674941918776146</v>
+        <v>-3.956812273164932</v>
       </c>
       <c r="G80">
-        <v>-2.573529868168194</v>
+        <v>-11.11272123725444</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>5.395345861180497</v>
       </c>
       <c r="E81">
-        <v>-17.28583040729444</v>
+        <v>-27.79122441941055</v>
       </c>
       <c r="F81">
-        <v>-3.91158242407294</v>
+        <v>-4.658551572443193</v>
       </c>
       <c r="G81">
-        <v>-1.953845401399717</v>
+        <v>-9.914770538959308</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>5.629434074788502</v>
       </c>
       <c r="E82">
-        <v>-19.69333474331029</v>
+        <v>-29.10129383593355</v>
       </c>
       <c r="F82">
-        <v>-3.826710040358624</v>
+        <v>-4.903883455803919</v>
       </c>
       <c r="G82">
-        <v>-3.528883789345534</v>
+        <v>-12.92509263491061</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>5.841680004565026</v>
       </c>
       <c r="E83">
-        <v>-18.9721254443747</v>
+        <v>-29.20358300681881</v>
       </c>
       <c r="F83">
-        <v>-3.86284387452529</v>
+        <v>-4.272071107515971</v>
       </c>
       <c r="G83">
-        <v>-2.052608906472794</v>
+        <v>-11.77215542431295</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>6.026946786707239</v>
       </c>
       <c r="E84">
-        <v>-20.29202164949435</v>
+        <v>-29.96614180191844</v>
       </c>
       <c r="F84">
-        <v>-4.126322652118078</v>
+        <v>-4.417895580797804</v>
       </c>
       <c r="G84">
-        <v>-2.98881463225099</v>
+        <v>-10.988890281358</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>6.181948510089581</v>
       </c>
       <c r="E85">
-        <v>-21.33285064389131</v>
+        <v>-31.07403523213199</v>
       </c>
       <c r="F85">
-        <v>-3.486692339578563</v>
+        <v>-4.459194671807676</v>
       </c>
       <c r="G85">
-        <v>-2.687538435449615</v>
+        <v>-11.1078282509474</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>6.299728720414731</v>
       </c>
       <c r="E86">
-        <v>-21.29953466061688</v>
+        <v>-30.41898014573746</v>
       </c>
       <c r="F86">
-        <v>-4.607397079521542</v>
+        <v>-4.645090864014916</v>
       </c>
       <c r="G86">
-        <v>-3.594482249206193</v>
+        <v>-9.851022674055102</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>6.376986410077913</v>
       </c>
       <c r="E87">
-        <v>-23.88377628020409</v>
+        <v>-32.48410920440338</v>
       </c>
       <c r="F87">
-        <v>-4.118142811064834</v>
+        <v>-5.152934672507053</v>
       </c>
       <c r="G87">
-        <v>-3.647199376373547</v>
+        <v>-11.54752166729124</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>6.405799061244137</v>
       </c>
       <c r="E88">
-        <v>-23.62191274223654</v>
+        <v>-32.93284701500846</v>
       </c>
       <c r="F88">
-        <v>-3.701378721622577</v>
+        <v>-4.347439672031734</v>
       </c>
       <c r="G88">
-        <v>-2.721445042862831</v>
+        <v>-11.58280877219433</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>6.381083034027517</v>
       </c>
       <c r="E89">
-        <v>-25.69541947781666</v>
+        <v>-34.73647028515344</v>
       </c>
       <c r="F89">
-        <v>-3.945136401303355</v>
+        <v>-5.023822255897894</v>
       </c>
       <c r="G89">
-        <v>-2.011078112682637</v>
+        <v>-11.3342066654683</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>6.296879201803348</v>
       </c>
       <c r="E90">
-        <v>-26.73465444936292</v>
+        <v>-35.9655705864193</v>
       </c>
       <c r="F90">
-        <v>-4.379287997991221</v>
+        <v>-5.303537978388725</v>
       </c>
       <c r="G90">
-        <v>-1.998173606170558</v>
+        <v>-11.45332340451682</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>6.146373233748665</v>
       </c>
       <c r="E91">
-        <v>-27.72797975141942</v>
+        <v>-36.4287225297908</v>
       </c>
       <c r="F91">
-        <v>-4.288987462251737</v>
+        <v>-5.4310057164047</v>
       </c>
       <c r="G91">
-        <v>-2.483307570586437</v>
+        <v>-10.38071989197511</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>5.926935261995531</v>
       </c>
       <c r="E92">
-        <v>-29.84148423367229</v>
+        <v>-37.50340186739509</v>
       </c>
       <c r="F92">
-        <v>-4.042519269896684</v>
+        <v>-4.689151146288357</v>
       </c>
       <c r="G92">
-        <v>-1.935329520198573</v>
+        <v>-10.63791948546663</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>5.631068399480441</v>
       </c>
       <c r="E93">
-        <v>-31.29422548804395</v>
+        <v>-38.70900165279814</v>
       </c>
       <c r="F93">
-        <v>-4.32120162427769</v>
+        <v>-5.369359171793262</v>
       </c>
       <c r="G93">
-        <v>-2.744648656547583</v>
+        <v>-11.18954906758431</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>5.259370844147274</v>
       </c>
       <c r="E94">
-        <v>-33.79002374602435</v>
+        <v>-40.08852427517679</v>
       </c>
       <c r="F94">
-        <v>-4.054753398093454</v>
+        <v>-4.582962872805184</v>
       </c>
       <c r="G94">
-        <v>-2.703667413316945</v>
+        <v>-11.54611799598259</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>4.813579388369573</v>
       </c>
       <c r="E95">
-        <v>-35.233314075142</v>
+        <v>-41.69904888516071</v>
       </c>
       <c r="F95">
-        <v>-4.644805005097179</v>
+        <v>-5.315408646077901</v>
       </c>
       <c r="G95">
-        <v>-3.604526444372341</v>
+        <v>-10.6581071921651</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>4.287913436328203</v>
       </c>
       <c r="E96">
-        <v>-38.07852033060623</v>
+        <v>-45.66547813408007</v>
       </c>
       <c r="F96">
-        <v>-4.521975149854569</v>
+        <v>-4.896481214355155</v>
       </c>
       <c r="G96">
-        <v>-4.73463082238565</v>
+        <v>-11.30596440147278</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>3.70169607015577</v>
       </c>
       <c r="E97">
-        <v>-40.022524030752</v>
+        <v>-46.03429290692377</v>
       </c>
       <c r="F97">
-        <v>-4.198785908131968</v>
+        <v>-4.933858257665441</v>
       </c>
       <c r="G97">
-        <v>-3.494752064835648</v>
+        <v>-11.32503314377898</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>3.042221311601265</v>
       </c>
       <c r="E98">
-        <v>-42.06806970357176</v>
+        <v>-47.33726394043975</v>
       </c>
       <c r="F98">
-        <v>-4.877737262992971</v>
+        <v>-4.953508088811255</v>
       </c>
       <c r="G98">
-        <v>-4.137564002741474</v>
+        <v>-12.40190394952081</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>2.348887568121273</v>
       </c>
       <c r="E99">
-        <v>-43.24690167911547</v>
+        <v>-49.413204730799</v>
       </c>
       <c r="F99">
-        <v>-4.366639730697564</v>
+        <v>-4.910797915830727</v>
       </c>
       <c r="G99">
-        <v>-4.498618720345468</v>
+        <v>-12.2008147923744</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>1.594497786386539</v>
       </c>
       <c r="E100">
-        <v>-46.57199032517253</v>
+        <v>-50.52136081250499</v>
       </c>
       <c r="F100">
-        <v>-4.400671195261484</v>
+        <v>-4.705791936194837</v>
       </c>
       <c r="G100">
-        <v>-3.994621267446823</v>
+        <v>-11.10738463784514</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>0.8562211709978874</v>
       </c>
       <c r="E101">
-        <v>-48.48629516065748</v>
+        <v>-52.01607309609825</v>
       </c>
       <c r="F101">
-        <v>-4.573118556834813</v>
+        <v>-5.062835267418829</v>
       </c>
       <c r="G101">
-        <v>-4.987973630323917</v>
+        <v>-12.54011591523984</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>0.04275389307046659</v>
       </c>
       <c r="E102">
-        <v>-50.34900709177306</v>
+        <v>-53.90867861625696</v>
       </c>
       <c r="F102">
-        <v>-4.542189572159238</v>
+        <v>-4.897627817437932</v>
       </c>
       <c r="G102">
-        <v>-5.915303783511327</v>
+        <v>-12.65263142648305</v>
       </c>
     </row>
   </sheetData>
